--- a/docs/workbook.xlsx
+++ b/docs/workbook.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Modules"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
   <si>
     <t>Entity yang dibutuhkan</t>
   </si>
@@ -28,15 +28,6 @@
     <t>ERD</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>Kode</t>
   </si>
   <si>
@@ -59,48 +50,6 @@
   </si>
   <si>
     <t>Entity/Objek Terkait</t>
-  </si>
-  <si>
-    <t>UC-N01</t>
-  </si>
-  <si>
-    <t>Export laporan bulanan ke Excel</t>
-  </si>
-  <si>
-    <t>Reporting</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Permintaan owner di luar proses BPMN utama, untuk audit internal</t>
-  </si>
-  <si>
-    <t>File Excel</t>
-  </si>
-  <si>
-    <t>Sales Order</t>
-  </si>
-  <si>
-    <t>UC-01</t>
-  </si>
-  <si>
-    <t>Generate repeat order</t>
-  </si>
-  <si>
-    <t>Generate quotation berdasarkan order sebelumnya</t>
-  </si>
-  <si>
-    <t>Quotation</t>
-  </si>
-  <si>
-    <t>Quotation, Quotation Detail</t>
-  </si>
-  <si>
-    <t>Penjualan, quotation, konfirmasi order</t>
-  </si>
-  <si>
-    <t>Sales Lead</t>
   </si>
 </sst>
 </file>
@@ -108,7 +57,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,13 +67,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF808080"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -142,7 +85,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -165,13 +108,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -181,14 +117,14 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -495,34 +431,23 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="40.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="2" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="40.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="16.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -535,7 +460,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="5" width="8.005" customWidth="1" bestFit="1"/>
@@ -550,55 +475,89 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -610,69 +569,43 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="26.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="32.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="2" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="26.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="32.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="28.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -685,12 +618,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="2" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="8.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -704,17 +637,6 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
